--- a/Data/EmployeeManagement.xlsx
+++ b/Data/EmployeeManagement.xlsx
@@ -1,18 +1,3 @@
-
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data1" sheetId="1" state="visible" r:id="rId1"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
-</file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -50,7 +35,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -125,8 +110,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Employee_Table" displayName="Employee_Table" ref="A1:D31" headerRowCount="1">
-  <autoFilter ref="A1:D16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Employee_Table" displayName="Employee_Table" ref="A1:D61" headerRowCount="1">
+  <autoFilter ref="A1:D46"/>
   <tableColumns count="4">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Name"/>
@@ -426,8 +411,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -988,6 +973,546 @@
       <c r="D31" t="inlineStr">
         <is>
           <t>Avestan</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>150</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deborah Rose</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>54</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Malay</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Edward Ray</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>61</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Indonesian</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>78</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Christine Morrow</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>48</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Assamese</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>290</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Courtney Castro</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>42</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Russian</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>655</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Steven Miller</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>31</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Bengali</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>98</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Marcus Bates</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>61</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Amharic</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>557</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Abigail Dominguez</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>20</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Panjabi</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>60</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Rebecca James</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>29</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Ossetian</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>729</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Gary Fry MD</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>38</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Albanian</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>678</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Shane White</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>21</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Tigrinya</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>19</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Joseph Miller</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>51</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Inuktitut</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>614</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Kimberly Ball</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>33</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Manx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>689</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Thomas Woods</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>23</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Twi</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>835</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Lance Williams</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>52</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Breton</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>755</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Devon Martin</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>38</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Kinyarwanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>794</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Nathaniel Hunter</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>29</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Hebrew</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>909</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Timothy Wilkinson</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>29</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Albanian</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>710</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>David Green</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>21</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>977</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Margaret Garcia</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>36</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Komi</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>511</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Jimmy Melendez</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>56</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Lithuanian</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>876</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Jon Kelley</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>26</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sotho, Southern</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>877</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Diane Summers</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>30</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>427</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Emily Russell</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>65</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Gaelic</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>661</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Joseph Shannon</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>64</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Tajik</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>206</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Christopher Wells</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>31</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Kongo</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>27</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Anthony Rivera</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>46</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Kazakh</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>816</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Zachary Hartman</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>63</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Malay</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>940</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>William Johnson Jr.</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>28</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Amharic</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>954</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>John Guzman</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>52</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Maori</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>896</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Marc Morgan</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>21</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Malay</t>
         </is>
       </c>
     </row>

--- a/Data/EmployeeManagement.xlsx
+++ b/Data/EmployeeManagement.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Next Sheet" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -125,16 +124,33 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Nikish Daniel</author>
+  </authors>
+  <commentList>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>This is a Comment</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Employee_Table" displayName="Employee_Table" ref="A1:D16" headerRowCount="1">
-  <autoFilter ref="A1:D16"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Employee_Table" displayName="Employee_Table" ref="A1:F31" headerRowCount="1">
+  <autoFilter ref="A1:F16"/>
+  <tableColumns count="6">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Name"/>
     <tableColumn id="3" name="Age"/>
     <tableColumn id="4" name="Languages Known"/>
+    <tableColumn id="5" name="Gender"/>
+    <tableColumn id="6" name="Comments"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
 </table>
 </file>
 
@@ -427,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,294 +467,598 @@
           <t>Languages Known</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>325</v>
+        <v>738</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Andrea Swanson</t>
+          <t>Rodney Jensen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Kikuyu</t>
-        </is>
-      </c>
+          <t>Venda</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>759</v>
+        <v>716</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Charles Webster</t>
+          <t>Alexis Poole</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Navajo</t>
+          <t>Twi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>937</v>
+        <v>538</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Timothy Smith</t>
+          <t>Rebecca Serrano</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Breton</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>205</v>
+        <v>798</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ivan Hubbard</t>
+          <t>Tara Thomas</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Norwegian Nynorsk</t>
+          <t>Pali</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>514</v>
+        <v>803</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rebecca Alvarado</t>
+          <t>Nicholas Williams</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bihari languages</t>
+          <t>Faroese</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Craig Poole</t>
+          <t>Colleen Washington</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ukrainian</t>
+          <t>Uzbek</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>931</v>
+        <v>171</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Michael Evans</t>
+          <t>Rebecca Armstrong</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ukrainian</t>
+          <t>Korean</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>177</v>
+        <v>566</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nicole Miller</t>
+          <t>Kendra Brown</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Greek</t>
+          <t>Oromo</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>848</v>
+        <v>323</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Terri Patel</t>
+          <t>Dakota Anderson</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Danish</t>
+          <t>Serbian</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>52</v>
+        <v>993</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Michael Villarreal</t>
+          <t>Holly West</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nepali</t>
+          <t>Kurdish</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>936</v>
+        <v>401</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Beverly Gray</t>
+          <t>Chloe Bartlett</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Czech</t>
+          <t>Inupiaq</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lisa Torres</t>
+          <t>Pamela Lucas</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Dzongkha</t>
+          <t>Armenian</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>704</v>
+        <v>379</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Paul Oneal</t>
+          <t>Megan Rodriguez</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Lithuanian</t>
+          <t>Finnish</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>718</v>
+        <v>19</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lawrence Pennington</t>
+          <t>Christy Carter</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Romanian</t>
+          <t>Slovenian</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>934</v>
+        <v>192</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Michael Steele</t>
+          <t>Kathleen Jarvis</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sardinian</t>
-        </is>
-      </c>
+          <t>Quechua</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>395</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Miranda Simmons</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>70</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Twi</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>392</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Michelle Estes</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>54</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Wolof</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>200</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Jesus Mcdonald</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>37</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ido</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>542</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Stephen Anderson</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>65</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Avestan</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>574</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>James Todd</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>26</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Zulu</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>690</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Michael Lopez</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>41</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Chichewa</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>294</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Melissa Hernandez</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>35</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>735</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Alan Rocha</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>60</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Dutch</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>635</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Jason Baker</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>49</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Swedish</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>631</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dr. Michelle Mills</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>43</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Kashmiri</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>736</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Donna Carey</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>26</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Twi</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>408</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>William Watkins</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>35</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bengali</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>644</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kevin Watson</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>57</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Malay</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>15</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Lindsay Gilbert</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>50</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Oriya</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>282</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Veronica Stevens</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>37</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Assamese</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Male,Female"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>